--- a/docs/viora-sku-template.xlsx
+++ b/docs/viora-sku-template.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -752,7 +752,62 @@
       <c r="A24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>BLENDS vs STACKS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Blend = one vial containing multiple peptides (Wolverine = BPC + TB-500 in one vial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Stack = multiple separate vials sold as a bundle (Premium Weight Loss = 3 separate vials)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>STACK COMPOSITION QUESTIONS to resolve:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Gut Health Stack currently includes Teduglutide which we're removing — pick a replacement or kill the stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Hormone Signaling Stack — 'Hormone' tag was removed on the call. Kill the stack or just rename it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Mood &amp; Balance + Intimacy Research stacks both contain Oxytocin (REMOVE candidate). Kill the stacks or restructure without Oxytocin?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Send the completed sheet back to Farris. He'll bulk-update the storefront, COA registry, and label generation from it in one batch.</t>
         </is>
@@ -1029,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2182,11 @@
           <t>10mg + 10mg</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Longevity</t>
@@ -2142,7 +2201,7 @@
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Per call: both at 10mg, not 5+5</t>
+          <t>Current price $75. Per call: both at 10mg, not 5+5</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2226,11 @@
           <t>10mg + 10mg</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Longevity</t>
@@ -2182,7 +2245,7 @@
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Both at 10mg per call</t>
+          <t>Current price $75. Both at 10mg per call</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2270,11 @@
           <t>?</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Anti-Aging</t>
@@ -2222,169 +2289,565 @@
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>DOSAGE? Need component breakdown from Marvin</t>
+          <t>Current price $85. DOSAGE? Need component breakdown from Marvin</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>STK-PREMWL</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Viora Premium Weight Loss Stack</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>VH3-R + Tesamorelin + MOTS-c</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3 vials</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Best Seller, Weight Loss</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Current price $388. Confirm components + dose mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>STK-WL</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Viora Weight Loss Stack</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Tesamorelin + VH3-R</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2 vials</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Weight Loss</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Current price $303</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>STK-MET</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Viora Metabolic Stack</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>VH3-R + MOTS-c + NAD+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>3 vials</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Current price $430. NOTE: 'Metabolic Health' tag removed — using 'Energy' instead. Confirm or kill?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>STK-GUT</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Viora Gut Health Stack</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>BPC-157 + GLP-2 (Teduglutide)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2 vials</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Longevity</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Current price $265. ⚠️ Includes Teduglutide which we're removing — replace with what?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>STK-LNG</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Viora Longevity Stack</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>NAD+ + MOTS-c + GHK-Cu</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>3 vials</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Longevity, Anti-Aging</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Current price $189</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>STK-HORM</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Viora Hormone Signaling Stack</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Tesamorelin + Ipamorelin + IGF-1 LR3</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3 vials</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>REMOVE?</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Current price $102. ⚠️ 'Hormone' tag removed per call. Kill this stack or rename?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>STK-MOOD</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Viora Mood &amp; Balance Stack</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Selank + Semax + Oxytocin</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3 vials</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Current price $70. ⚠️ Contains Oxytocin (REMOVE candidate). Keep without Oxytocin? Or drop entire stack?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>STK-INT</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Viora Intimacy Research Stack</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>PT-141 + Oxytocin</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2 vials</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>REMOVE?</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Current price $50. ⚠️ Contains Oxytocin (REMOVE candidate). Kill?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>STK-CEO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Viora CEO Stack</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>NAD+ + Semax + Selank</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3 vials</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive, Energy</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>stack</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Current price $100. Confirm — performance positioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>REMOVE-1</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>GLP-2 (Teduglutide)</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Teduglutide</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>5mg</t>
         </is>
       </c>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>REMOVE</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>223132-37-4</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Decision: replace with Tirzepatide (VH2-T)? Or keep both?</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>REMOVE-2</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Oxytocin</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Oxytocin</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>2mg</t>
         </is>
       </c>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>REMOVE?</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>50-56-6</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Was in catalog — keep or drop?</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Was in catalog — keep or drop? Affects 3 stacks (Mood, Intimacy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>REMOVE-3</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>DSIP</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>DSIP</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>REMOVE</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>62568-57-4</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>Confirmed NOT in inventory per Jordan — remove</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>REMOVE-4</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>5-Amino 1MQ</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>5-Amino 1MQ</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>REMOVE</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Confirmed NOT in inventory per Jordan — remove</t>
         </is>
